--- a/Bases_de_Dados/FootyStats/France National_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France National_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.09</v>
@@ -3748,7 +3748,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.8</v>
@@ -7018,7 +7018,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR30" t="n">
         <v>1.67</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.4</v>
@@ -9631,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ42" t="n">
         <v>1</v>
@@ -9852,7 +9852,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR43" t="n">
         <v>1.59</v>
@@ -13773,7 +13773,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.73</v>
@@ -14648,7 +14648,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR65" t="n">
         <v>1.23</v>
@@ -17697,7 +17697,7 @@
         <v>1.25</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.82</v>
@@ -19880,7 +19880,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR89" t="n">
         <v>1.52</v>
@@ -24019,7 +24019,7 @@
         <v>1.67</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.45</v>
@@ -26420,7 +26420,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR119" t="n">
         <v>1.25</v>
@@ -27507,7 +27507,7 @@
         <v>2</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.82</v>
@@ -29908,7 +29908,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR135" t="n">
         <v>1.51</v>
@@ -31649,7 +31649,7 @@
         <v>1.56</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.75</v>
@@ -33396,7 +33396,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR151" t="n">
         <v>1.34</v>
@@ -33829,7 +33829,7 @@
         <v>1.22</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.2</v>
@@ -37102,7 +37102,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AR168" t="n">
         <v>1.17</v>
@@ -40448,6 +40448,224 @@
       </c>
       <c r="BP183" t="n">
         <v>1.06</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>8010501</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F184" t="n">
+        <v>23</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="n">
+        <v>2</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="R184" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S184" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V184" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X184" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France National_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France National_20252026.xlsx
@@ -39076,22 +39076,22 @@
         <v>2.6</v>
       </c>
       <c r="AU177" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW177" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ177" t="n">
         <v>5</v>
-      </c>
-      <c r="AY177" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ177" t="n">
-        <v>6</v>
       </c>
       <c r="BA177" t="n">
         <v>9</v>
@@ -39294,19 +39294,19 @@
         <v>2.12</v>
       </c>
       <c r="AU178" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV178" t="n">
         <v>2</v>
       </c>
       <c r="AW178" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX178" t="n">
         <v>3</v>
       </c>
       <c r="AY178" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ178" t="n">
         <v>5</v>
@@ -39512,19 +39512,19 @@
         <v>2.57</v>
       </c>
       <c r="AU179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV179" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW179" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY179" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ179" t="n">
         <v>9</v>
@@ -39730,22 +39730,22 @@
         <v>2.63</v>
       </c>
       <c r="AU180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV180" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW180" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX180" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY180" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ180" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ180" t="n">
-        <v>8</v>
       </c>
       <c r="BA180" t="n">
         <v>2</v>
@@ -40166,22 +40166,22 @@
         <v>3.03</v>
       </c>
       <c r="AU182" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV182" t="n">
         <v>4</v>
       </c>
-      <c r="AV182" t="n">
-        <v>3</v>
-      </c>
       <c r="AW182" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX182" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY182" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ182" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA182" t="n">
         <v>6</v>
@@ -40387,19 +40387,19 @@
         <v>4</v>
       </c>
       <c r="AV183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX183" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY183" t="n">
         <v>6</v>
       </c>
-      <c r="AY183" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ183" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA183" t="n">
         <v>2</v>
@@ -40605,19 +40605,19 @@
         <v>5</v>
       </c>
       <c r="AV184" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW184" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX184" t="n">
         <v>7</v>
       </c>
       <c r="AY184" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ184" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA184" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/France National_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France National_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP184"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.91</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.27</v>
@@ -1568,7 +1568,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.45</v>
@@ -3094,7 +3094,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.82</v>
@@ -3530,7 +3530,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.5</v>
@@ -4399,10 +4399,10 @@
         <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR18" t="n">
         <v>1.86</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.91</v>
@@ -4838,7 +4838,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
         <v>1.25</v>
@@ -5274,7 +5274,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.53</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR23" t="n">
         <v>1.58</v>
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.27</v>
@@ -5925,10 +5925,10 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR25" t="n">
         <v>1.77</v>
@@ -6582,7 +6582,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR28" t="n">
         <v>1.27</v>
@@ -6797,7 +6797,7 @@
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.27</v>
@@ -7018,7 +7018,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR30" t="n">
         <v>1.67</v>
@@ -7669,10 +7669,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR33" t="n">
         <v>0.9399999999999999</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.91</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.45</v>
@@ -8323,10 +8323,10 @@
         <v>0.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>1.33</v>
@@ -8541,10 +8541,10 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR37" t="n">
         <v>1.8</v>
@@ -8762,7 +8762,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR38" t="n">
         <v>1.4</v>
@@ -8977,7 +8977,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.75</v>
@@ -9198,7 +9198,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR40" t="n">
         <v>1.05</v>
@@ -9852,7 +9852,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR43" t="n">
         <v>1.59</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.45</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.91</v>
@@ -11375,10 +11375,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR50" t="n">
         <v>0.82</v>
@@ -11593,10 +11593,10 @@
         <v>2</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR51" t="n">
         <v>1.46</v>
@@ -11811,7 +11811,7 @@
         <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.75</v>
@@ -12029,10 +12029,10 @@
         <v>0.33</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12247,10 +12247,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR54" t="n">
         <v>1.23</v>
@@ -12465,10 +12465,10 @@
         <v>3</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR55" t="n">
         <v>1.8</v>
@@ -12686,7 +12686,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -14645,10 +14645,10 @@
         <v>2.33</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR65" t="n">
         <v>1.23</v>
@@ -14863,7 +14863,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.75</v>
@@ -15081,10 +15081,10 @@
         <v>1.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR67" t="n">
         <v>0.98</v>
@@ -15299,10 +15299,10 @@
         <v>1.33</v>
       </c>
       <c r="AP68" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ68" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>1.4</v>
       </c>
       <c r="AR68" t="n">
         <v>1.48</v>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR69" t="n">
         <v>1.42</v>
@@ -15735,10 +15735,10 @@
         <v>1.67</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ70" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR70" t="n">
         <v>1.74</v>
@@ -15953,10 +15953,10 @@
         <v>2.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR71" t="n">
         <v>0.66</v>
@@ -16171,10 +16171,10 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR72" t="n">
         <v>0.9399999999999999</v>
@@ -16828,7 +16828,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR75" t="n">
         <v>1.56</v>
@@ -17261,7 +17261,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ77" t="n">
         <v>1</v>
@@ -18351,7 +18351,7 @@
         <v>1.2</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.75</v>
@@ -18569,10 +18569,10 @@
         <v>1</v>
       </c>
       <c r="AP83" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ83" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>1.55</v>
       </c>
       <c r="AR83" t="n">
         <v>0.98</v>
@@ -18790,7 +18790,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR84" t="n">
         <v>1.57</v>
@@ -19005,10 +19005,10 @@
         <v>0.5</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR85" t="n">
         <v>1.48</v>
@@ -19223,7 +19223,7 @@
         <v>0.25</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.73</v>
@@ -19441,10 +19441,10 @@
         <v>1.25</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR87" t="n">
         <v>1.23</v>
@@ -19659,10 +19659,10 @@
         <v>1.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR88" t="n">
         <v>0.6</v>
@@ -19877,10 +19877,10 @@
         <v>2.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR89" t="n">
         <v>1.52</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ90" t="n">
         <v>1</v>
@@ -20316,7 +20316,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR91" t="n">
         <v>1.52</v>
@@ -20534,7 +20534,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR92" t="n">
         <v>1.38</v>
@@ -21403,7 +21403,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.82</v>
@@ -21839,10 +21839,10 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR98" t="n">
         <v>1.3</v>
@@ -22057,7 +22057,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.7</v>
@@ -22278,7 +22278,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR100" t="n">
         <v>1.56</v>
@@ -22493,10 +22493,10 @@
         <v>1.4</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR101" t="n">
         <v>1.25</v>
@@ -22711,7 +22711,7 @@
         <v>0.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.73</v>
@@ -22929,10 +22929,10 @@
         <v>1.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR103" t="n">
         <v>0.96</v>
@@ -23365,10 +23365,10 @@
         <v>1.8</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ105" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR105" t="n">
         <v>0.84</v>
@@ -23586,7 +23586,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR106" t="n">
         <v>1.39</v>
@@ -23804,7 +23804,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR107" t="n">
         <v>1.64</v>
@@ -24673,7 +24673,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.5</v>
@@ -24891,7 +24891,7 @@
         <v>0.83</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ112" t="n">
         <v>1</v>
@@ -25112,7 +25112,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR113" t="n">
         <v>1.09</v>
@@ -25327,7 +25327,7 @@
         <v>0.17</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.73</v>
@@ -25548,7 +25548,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR115" t="n">
         <v>1.59</v>
@@ -25766,7 +25766,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR116" t="n">
         <v>1.59</v>
@@ -25984,7 +25984,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR117" t="n">
         <v>1.51</v>
@@ -26199,10 +26199,10 @@
         <v>1.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR118" t="n">
         <v>0.97</v>
@@ -26417,10 +26417,10 @@
         <v>2.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ119" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR119" t="n">
         <v>1.25</v>
@@ -26635,7 +26635,7 @@
         <v>1.14</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.75</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.82</v>
@@ -27289,7 +27289,7 @@
         <v>1.25</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.27</v>
@@ -27510,7 +27510,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR124" t="n">
         <v>1.58</v>
@@ -27725,7 +27725,7 @@
         <v>0.71</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ125" t="n">
         <v>1</v>
@@ -27946,7 +27946,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ126" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR126" t="n">
         <v>1.22</v>
@@ -28161,7 +28161,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.45</v>
@@ -28382,7 +28382,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR128" t="n">
         <v>1.47</v>
@@ -29036,7 +29036,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR131" t="n">
         <v>1.31</v>
@@ -29251,7 +29251,7 @@
         <v>0.33</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.7</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.82</v>
@@ -29690,7 +29690,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -29908,7 +29908,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR135" t="n">
         <v>1.51</v>
@@ -30123,7 +30123,7 @@
         <v>0.29</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.73</v>
@@ -30344,7 +30344,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR137" t="n">
         <v>1.54</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.45</v>
@@ -30780,7 +30780,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR139" t="n">
         <v>1.43</v>
@@ -30995,10 +30995,10 @@
         <v>1.75</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR140" t="n">
         <v>1.42</v>
@@ -31213,10 +31213,10 @@
         <v>1.25</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR141" t="n">
         <v>1.01</v>
@@ -31431,7 +31431,7 @@
         <v>0.67</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.91</v>
@@ -31870,7 +31870,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ144" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR144" t="n">
         <v>1.46</v>
@@ -32742,7 +32742,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR148" t="n">
         <v>1.21</v>
@@ -32957,7 +32957,7 @@
         <v>0.14</v>
       </c>
       <c r="AP149" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.5</v>
@@ -33175,7 +33175,7 @@
         <v>0.89</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ150" t="n">
         <v>1</v>
@@ -33396,7 +33396,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR151" t="n">
         <v>1.34</v>
@@ -33614,7 +33614,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR152" t="n">
         <v>1.69</v>
@@ -33832,7 +33832,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR153" t="n">
         <v>1.5</v>
@@ -34047,10 +34047,10 @@
         <v>1.67</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR154" t="n">
         <v>1.48</v>
@@ -34265,7 +34265,7 @@
         <v>1.7</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.75</v>
@@ -34483,10 +34483,10 @@
         <v>1.89</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ156" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR156" t="n">
         <v>1.39</v>
@@ -34701,10 +34701,10 @@
         <v>1.63</v>
       </c>
       <c r="AP157" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR157" t="n">
         <v>0.9399999999999999</v>
@@ -34922,7 +34922,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR158" t="n">
         <v>1.37</v>
@@ -35137,7 +35137,7 @@
         <v>1.78</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.45</v>
@@ -35355,10 +35355,10 @@
         <v>1.89</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR160" t="n">
         <v>1.11</v>
@@ -35573,7 +35573,7 @@
         <v>1.22</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.27</v>
@@ -35791,7 +35791,7 @@
         <v>1.1</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ162" t="n">
         <v>1</v>
@@ -36230,7 +36230,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR164" t="n">
         <v>1.42</v>
@@ -37102,7 +37102,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ168" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR168" t="n">
         <v>1.17</v>
@@ -37317,10 +37317,10 @@
         <v>1.5</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR169" t="n">
         <v>1.45</v>
@@ -37535,7 +37535,7 @@
         <v>1.64</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.75</v>
@@ -37756,7 +37756,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR171" t="n">
         <v>1.43</v>
@@ -37971,10 +37971,10 @@
         <v>1.7</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR172" t="n">
         <v>1.52</v>
@@ -38189,10 +38189,10 @@
         <v>1.4</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR173" t="n">
         <v>1.03</v>
@@ -38407,7 +38407,7 @@
         <v>0.7</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.91</v>
@@ -38625,10 +38625,10 @@
         <v>2</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ175" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AR175" t="n">
         <v>1.11</v>
@@ -38843,10 +38843,10 @@
         <v>0.78</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR176" t="n">
         <v>1.36</v>
@@ -40369,7 +40369,7 @@
         <v>1</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AQ183" t="n">
         <v>1</v>
@@ -40590,7 +40590,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ184" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR184" t="n">
         <v>1.49</v>
@@ -40666,6 +40666,1750 @@
       </c>
       <c r="BP184" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>8010505</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F185" t="n">
+        <v>24</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Châteauroux</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>2</v>
+      </c>
+      <c r="N185" t="n">
+        <v>3</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>['58', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R185" t="n">
+        <v>2</v>
+      </c>
+      <c r="S185" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U185" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V185" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W185" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X185" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>8010504</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F186" t="n">
+        <v>24</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Aubagne</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Fleury 91</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>1</v>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>2</v>
+      </c>
+      <c r="N186" t="n">
+        <v>3</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>['45+4', '54']</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R186" t="n">
+        <v>2</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T186" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V186" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="W186" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X186" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>8010503</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F187" t="n">
+        <v>24</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bourg-en-Bresse</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>4</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['63', '67', '90+3']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R187" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S187" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V187" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X187" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8010502</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F188" t="n">
+        <v>24</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Paris 13 Atletico</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Le Puy F.43 Auvergne</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>4</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S188" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V188" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X188" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8010535</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F189" t="n">
+        <v>24</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Stade Briochin</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="n">
+        <v>3</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>3</v>
+      </c>
+      <c r="N189" t="n">
+        <v>4</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['1', '15', '26']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R189" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S189" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X189" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8010531</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F190" t="n">
+        <v>24</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Concarneau</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>1</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>4</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2</v>
+      </c>
+      <c r="S190" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V190" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X190" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8010525</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F191" t="n">
+        <v>24</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Villefranche</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>2</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>3</v>
+      </c>
+      <c r="L191" t="n">
+        <v>2</v>
+      </c>
+      <c r="M191" t="n">
+        <v>3</v>
+      </c>
+      <c r="N191" t="n">
+        <v>5</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['11', '45+2']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['10', '57', '63']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2</v>
+      </c>
+      <c r="S191" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X191" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>8010530</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46087.64583333334</v>
+      </c>
+      <c r="F192" t="n">
+        <v>24</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Quevilly Rouen</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Versailles</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>2</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" t="n">
+        <v>4</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['28', '69']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['39', '89']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>4</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S192" t="n">
+        <v>3</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V192" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X192" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/France National_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/France National_20252026.xlsx
@@ -40820,22 +40820,22 @@
         <v>2.51</v>
       </c>
       <c r="AU185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV185" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW185" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX185" t="n">
         <v>3</v>
       </c>
       <c r="AY185" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ185" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA185" t="n">
         <v>6</v>
@@ -41259,19 +41259,19 @@
         <v>6</v>
       </c>
       <c r="AV187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW187" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX187" t="n">
         <v>6</v>
       </c>
       <c r="AY187" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ187" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA187" t="n">
         <v>3</v>
@@ -41474,22 +41474,22 @@
         <v>2.59</v>
       </c>
       <c r="AU188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV188" t="n">
         <v>4</v>
       </c>
       <c r="AW188" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX188" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY188" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ188" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA188" t="n">
         <v>9</v>
@@ -41695,19 +41695,19 @@
         <v>1</v>
       </c>
       <c r="AV189" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW189" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY189" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ189" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ189" t="n">
-        <v>6</v>
       </c>
       <c r="BA189" t="n">
         <v>5</v>
@@ -41919,13 +41919,13 @@
         <v>6</v>
       </c>
       <c r="AX190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY190" t="n">
         <v>12</v>
       </c>
       <c r="AZ190" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA190" t="n">
         <v>3</v>
@@ -42137,13 +42137,13 @@
         <v>5</v>
       </c>
       <c r="AX191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY191" t="n">
         <v>9</v>
       </c>
       <c r="AZ191" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA191" t="n">
         <v>4</v>
@@ -42352,16 +42352,16 @@
         <v>5</v>
       </c>
       <c r="AW192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX192" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY192" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ192" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA192" t="n">
         <v>4</v>
